--- a/public/downloads/rolling-forecast-template.xlsx
+++ b/public/downloads/rolling-forecast-template.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rolling forecast" sheetId="1" r:id="Re7e3eefee1e340a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rolling forecast" sheetId="1" r:id="Re8d152c4d86b4643"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -529,7 +529,7 @@
     </x:row>
     <x:row r="14" ht="24" customHeight="1">
       <x:c r="A14" s="4" t="n">
-        <x:f>DATE(YEAR($B$5),MONTH($B$5)+1,1)</x:f>
+        <x:f>IF(ISNUMBER($B$5),IF($B$5&gt;0,DATE(YEAR($B$5),MONTH($B$5)+1,1),"Invalid cutoff"),"Invalid cutoff")</x:f>
         <x:v>46113</x:v>
       </x:c>
       <x:c r="B14" s="18" t="n">
@@ -571,7 +571,7 @@
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
       <x:c r="A15" s="4" t="n">
-        <x:f>DATE(YEAR($B$5),MONTH($B$5)+2,1)</x:f>
+        <x:f>IF(ISNUMBER($B$5),IF($B$5&gt;0,DATE(YEAR($B$5),MONTH($B$5)+2,1),"Invalid cutoff"),"Invalid cutoff")</x:f>
         <x:v>46143</x:v>
       </x:c>
       <x:c r="B15" s="18" t="n">
@@ -613,7 +613,7 @@
     </x:row>
     <x:row r="16" ht="24" customHeight="1">
       <x:c r="A16" s="4" t="n">
-        <x:f>DATE(YEAR($B$5),MONTH($B$5)+3,1)</x:f>
+        <x:f>IF(ISNUMBER($B$5),IF($B$5&gt;0,DATE(YEAR($B$5),MONTH($B$5)+3,1),"Invalid cutoff"),"Invalid cutoff")</x:f>
         <x:v>46174</x:v>
       </x:c>
       <x:c r="B16" s="18" t="n">
@@ -655,7 +655,7 @@
     </x:row>
     <x:row r="17" ht="24" customHeight="1">
       <x:c r="A17" s="4" t="n">
-        <x:f>DATE(YEAR($B$5),MONTH($B$5)+4,1)</x:f>
+        <x:f>IF(ISNUMBER($B$5),IF($B$5&gt;0,DATE(YEAR($B$5),MONTH($B$5)+4,1),"Invalid cutoff"),"Invalid cutoff")</x:f>
         <x:v>46204</x:v>
       </x:c>
       <x:c r="B17" s="18" t="n">
@@ -697,7 +697,7 @@
     </x:row>
     <x:row r="18" ht="24" customHeight="1">
       <x:c r="A18" s="4" t="n">
-        <x:f>DATE(YEAR($B$5),MONTH($B$5)+5,1)</x:f>
+        <x:f>IF(ISNUMBER($B$5),IF($B$5&gt;0,DATE(YEAR($B$5),MONTH($B$5)+5,1),"Invalid cutoff"),"Invalid cutoff")</x:f>
         <x:v>46235</x:v>
       </x:c>
       <x:c r="B18" s="18" t="n">
@@ -739,7 +739,7 @@
     </x:row>
     <x:row r="19" ht="24" customHeight="1">
       <x:c r="A19" s="4" t="n">
-        <x:f>DATE(YEAR($B$5),MONTH($B$5)+6,1)</x:f>
+        <x:f>IF(ISNUMBER($B$5),IF($B$5&gt;0,DATE(YEAR($B$5),MONTH($B$5)+6,1),"Invalid cutoff"),"Invalid cutoff")</x:f>
         <x:v>46266</x:v>
       </x:c>
       <x:c r="B19" s="18" t="n">
@@ -781,7 +781,7 @@
     </x:row>
     <x:row r="20" ht="24" customHeight="1">
       <x:c r="A20" s="4" t="n">
-        <x:f>DATE(YEAR($B$5),MONTH($B$5)+7,1)</x:f>
+        <x:f>IF(ISNUMBER($B$5),IF($B$5&gt;0,DATE(YEAR($B$5),MONTH($B$5)+7,1),"Invalid cutoff"),"Invalid cutoff")</x:f>
         <x:v>46296</x:v>
       </x:c>
       <x:c r="B20" s="18" t="n">
@@ -823,7 +823,7 @@
     </x:row>
     <x:row r="21" ht="24" customHeight="1">
       <x:c r="A21" s="4" t="n">
-        <x:f>DATE(YEAR($B$5),MONTH($B$5)+8,1)</x:f>
+        <x:f>IF(ISNUMBER($B$5),IF($B$5&gt;0,DATE(YEAR($B$5),MONTH($B$5)+8,1),"Invalid cutoff"),"Invalid cutoff")</x:f>
         <x:v>46327</x:v>
       </x:c>
       <x:c r="B21" s="18" t="n">
@@ -865,7 +865,7 @@
     </x:row>
     <x:row r="22" ht="24" customHeight="1">
       <x:c r="A22" s="4" t="n">
-        <x:f>DATE(YEAR($B$5),MONTH($B$5)+9,1)</x:f>
+        <x:f>IF(ISNUMBER($B$5),IF($B$5&gt;0,DATE(YEAR($B$5),MONTH($B$5)+9,1),"Invalid cutoff"),"Invalid cutoff")</x:f>
         <x:v>46357</x:v>
       </x:c>
       <x:c r="B22" s="18" t="n">
@@ -907,7 +907,7 @@
     </x:row>
     <x:row r="23" ht="24" customHeight="1">
       <x:c r="A23" s="4" t="n">
-        <x:f>DATE(YEAR($B$5),MONTH($B$5)+10,1)</x:f>
+        <x:f>IF(ISNUMBER($B$5),IF($B$5&gt;0,DATE(YEAR($B$5),MONTH($B$5)+10,1),"Invalid cutoff"),"Invalid cutoff")</x:f>
         <x:v>46388</x:v>
       </x:c>
       <x:c r="B23" s="18" t="n">
@@ -949,7 +949,7 @@
     </x:row>
     <x:row r="24" ht="24" customHeight="1">
       <x:c r="A24" s="4" t="n">
-        <x:f>DATE(YEAR($B$5),MONTH($B$5)+11,1)</x:f>
+        <x:f>IF(ISNUMBER($B$5),IF($B$5&gt;0,DATE(YEAR($B$5),MONTH($B$5)+11,1),"Invalid cutoff"),"Invalid cutoff")</x:f>
         <x:v>46419</x:v>
       </x:c>
       <x:c r="B24" s="18" t="n">
@@ -991,7 +991,7 @@
     </x:row>
     <x:row r="25" ht="24" customHeight="1">
       <x:c r="A25" s="4" t="n">
-        <x:f>DATE(YEAR($B$5),MONTH($B$5)+12,1)</x:f>
+        <x:f>IF(ISNUMBER($B$5),IF($B$5&gt;0,DATE(YEAR($B$5),MONTH($B$5)+12,1),"Invalid cutoff"),"Invalid cutoff")</x:f>
         <x:v>46447</x:v>
       </x:c>
       <x:c r="B25" s="18" t="n">
